--- a/artfynd/A 43989-2023 artfynd.xlsx
+++ b/artfynd/A 43989-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118504918</v>
+        <v>118504911</v>
       </c>
       <c r="B2" t="n">
-        <v>96801</v>
+        <v>97867</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>221952</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555017</v>
+        <v>555391</v>
       </c>
       <c r="R2" t="n">
-        <v>6954608</v>
+        <v>6954840</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118504911</v>
+        <v>118504918</v>
       </c>
       <c r="B3" t="n">
-        <v>97867</v>
+        <v>96801</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555391</v>
+        <v>555017</v>
       </c>
       <c r="R3" t="n">
-        <v>6954840</v>
+        <v>6954608</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 43989-2023 artfynd.xlsx
+++ b/artfynd/A 43989-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118504911</v>
+        <v>118504917</v>
       </c>
       <c r="B2" t="n">
-        <v>97867</v>
+        <v>57718</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,54 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221952</v>
+        <v>103001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stormyran, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555391</v>
+        <v>555355</v>
       </c>
       <c r="R2" t="n">
-        <v>6954840</v>
+        <v>6954810</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +793,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118504918</v>
+        <v>118504915</v>
       </c>
       <c r="B3" t="n">
-        <v>96801</v>
+        <v>97764</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +809,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>223591</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555017</v>
+        <v>555365</v>
       </c>
       <c r="R3" t="n">
-        <v>6954608</v>
+        <v>6954814</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118504907</v>
+        <v>118504914</v>
       </c>
       <c r="B4" t="n">
-        <v>97867</v>
+        <v>97764</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +911,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221952</v>
+        <v>223591</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +935,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>555127</v>
+        <v>555352</v>
       </c>
       <c r="R4" t="n">
-        <v>6954603</v>
+        <v>6954801</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +997,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118504920</v>
+        <v>118504927</v>
       </c>
       <c r="B5" t="n">
-        <v>96807</v>
+        <v>101230</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,20 +1009,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221941</v>
+        <v>221343</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Brunklöver</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Trifolium spadiceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1021,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>555004</v>
+        <v>555116</v>
       </c>
       <c r="R5" t="n">
-        <v>6954467</v>
+        <v>6954576</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,7 +1099,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118504909</v>
+        <v>118504911</v>
       </c>
       <c r="B6" t="n">
         <v>97867</v>
@@ -1123,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>555336</v>
+        <v>555391</v>
       </c>
       <c r="R6" t="n">
-        <v>6954786</v>
+        <v>6954840</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1201,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118504913</v>
+        <v>118504920</v>
       </c>
       <c r="B7" t="n">
-        <v>97764</v>
+        <v>96807</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1217,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>223591</v>
+        <v>221941</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1241,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>555342</v>
+        <v>555004</v>
       </c>
       <c r="R7" t="n">
-        <v>6954794</v>
+        <v>6954467</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1303,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118504917</v>
+        <v>118504912</v>
       </c>
       <c r="B8" t="n">
-        <v>57718</v>
+        <v>97764</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,54 +1315,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103001</v>
+        <v>223591</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stormyran, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>555355</v>
+        <v>555012</v>
       </c>
       <c r="R8" t="n">
-        <v>6954810</v>
+        <v>6954604</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1405,10 +1405,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118504924</v>
+        <v>118504913</v>
       </c>
       <c r="B9" t="n">
-        <v>97763</v>
+        <v>97764</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1421,21 +1421,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219790</v>
+        <v>223591</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1445,10 +1445,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>555097</v>
+        <v>555342</v>
       </c>
       <c r="R9" t="n">
-        <v>6954568</v>
+        <v>6954794</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1507,10 +1507,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118504915</v>
+        <v>118504918</v>
       </c>
       <c r="B10" t="n">
-        <v>97764</v>
+        <v>96801</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1523,21 +1523,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>223591</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1547,10 +1547,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>555365</v>
+        <v>555017</v>
       </c>
       <c r="R10" t="n">
-        <v>6954814</v>
+        <v>6954608</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1609,10 +1609,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118504912</v>
+        <v>118504921</v>
       </c>
       <c r="B11" t="n">
-        <v>97764</v>
+        <v>97763</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1625,21 +1625,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>223591</v>
+        <v>219790</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1649,10 +1649,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>555012</v>
+        <v>555045</v>
       </c>
       <c r="R11" t="n">
-        <v>6954604</v>
+        <v>6954595</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1711,10 +1711,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118504914</v>
+        <v>118504924</v>
       </c>
       <c r="B12" t="n">
-        <v>97764</v>
+        <v>97763</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1727,21 +1727,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>223591</v>
+        <v>219790</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1751,10 +1751,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>555352</v>
+        <v>555097</v>
       </c>
       <c r="R12" t="n">
-        <v>6954801</v>
+        <v>6954568</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1813,10 +1813,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118504925</v>
+        <v>118504909</v>
       </c>
       <c r="B13" t="n">
-        <v>97763</v>
+        <v>97867</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1829,21 +1829,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1853,10 +1853,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>555051</v>
+        <v>555336</v>
       </c>
       <c r="R13" t="n">
-        <v>6954472</v>
+        <v>6954786</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1915,7 +1915,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118504926</v>
+        <v>118504925</v>
       </c>
       <c r="B14" t="n">
         <v>97763</v>
@@ -1955,10 +1955,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>554994</v>
+        <v>555051</v>
       </c>
       <c r="R14" t="n">
-        <v>6954526</v>
+        <v>6954472</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2017,10 +2017,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118504921</v>
+        <v>118504907</v>
       </c>
       <c r="B15" t="n">
-        <v>97763</v>
+        <v>97867</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2033,21 +2033,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2057,10 +2057,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>555045</v>
+        <v>555127</v>
       </c>
       <c r="R15" t="n">
-        <v>6954595</v>
+        <v>6954603</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2119,10 +2119,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118504927</v>
+        <v>118504926</v>
       </c>
       <c r="B16" t="n">
-        <v>101230</v>
+        <v>97763</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2131,25 +2131,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221343</v>
+        <v>219790</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brunklöver</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Trifolium spadiceum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2159,10 +2159,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>555116</v>
+        <v>554994</v>
       </c>
       <c r="R16" t="n">
-        <v>6954576</v>
+        <v>6954526</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 43989-2023 artfynd.xlsx
+++ b/artfynd/A 43989-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118504917</v>
+        <v>118504914</v>
       </c>
       <c r="B2" t="n">
-        <v>57718</v>
+        <v>97764</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,54 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103001</v>
+        <v>223591</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stormyran, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555355</v>
+        <v>555352</v>
       </c>
       <c r="R2" t="n">
-        <v>6954810</v>
+        <v>6954801</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -793,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118504915</v>
+        <v>118504927</v>
       </c>
       <c r="B3" t="n">
-        <v>97764</v>
+        <v>101230</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>223591</v>
+        <v>221343</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Brunklöver</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Trifolium spadiceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -833,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555365</v>
+        <v>555116</v>
       </c>
       <c r="R3" t="n">
-        <v>6954814</v>
+        <v>6954576</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118504914</v>
+        <v>118504915</v>
       </c>
       <c r="B4" t="n">
         <v>97764</v>
@@ -935,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>555352</v>
+        <v>555365</v>
       </c>
       <c r="R4" t="n">
-        <v>6954801</v>
+        <v>6954814</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -997,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118504927</v>
+        <v>118504926</v>
       </c>
       <c r="B5" t="n">
-        <v>101230</v>
+        <v>97763</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221343</v>
+        <v>219790</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brunklöver</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Trifolium spadiceum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1037,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>555116</v>
+        <v>554994</v>
       </c>
       <c r="R5" t="n">
-        <v>6954576</v>
+        <v>6954526</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118504911</v>
+        <v>118504909</v>
       </c>
       <c r="B6" t="n">
         <v>97867</v>
@@ -1139,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>555391</v>
+        <v>555336</v>
       </c>
       <c r="R6" t="n">
-        <v>6954840</v>
+        <v>6954786</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1201,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118504920</v>
+        <v>118504912</v>
       </c>
       <c r="B7" t="n">
-        <v>96807</v>
+        <v>97764</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221941</v>
+        <v>223591</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1241,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>555004</v>
+        <v>555012</v>
       </c>
       <c r="R7" t="n">
-        <v>6954467</v>
+        <v>6954604</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1303,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118504912</v>
+        <v>118504917</v>
       </c>
       <c r="B8" t="n">
-        <v>97764</v>
+        <v>57718</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1315,38 +1299,54 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>223591</v>
+        <v>103001</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stormyran, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>555012</v>
+        <v>555355</v>
       </c>
       <c r="R8" t="n">
-        <v>6954604</v>
+        <v>6954810</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1405,10 +1405,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118504913</v>
+        <v>118504921</v>
       </c>
       <c r="B9" t="n">
-        <v>97764</v>
+        <v>97763</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1421,21 +1421,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>223591</v>
+        <v>219790</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1445,10 +1445,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>555342</v>
+        <v>555045</v>
       </c>
       <c r="R9" t="n">
-        <v>6954794</v>
+        <v>6954595</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1507,10 +1507,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118504918</v>
+        <v>118504924</v>
       </c>
       <c r="B10" t="n">
-        <v>96801</v>
+        <v>97763</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1523,21 +1523,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1547,10 +1547,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>555017</v>
+        <v>555097</v>
       </c>
       <c r="R10" t="n">
-        <v>6954608</v>
+        <v>6954568</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1609,10 +1609,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118504921</v>
+        <v>118504920</v>
       </c>
       <c r="B11" t="n">
-        <v>97763</v>
+        <v>96807</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1625,21 +1625,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219790</v>
+        <v>221941</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1649,10 +1649,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>555045</v>
+        <v>555004</v>
       </c>
       <c r="R11" t="n">
-        <v>6954595</v>
+        <v>6954467</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1711,10 +1711,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118504924</v>
+        <v>118504918</v>
       </c>
       <c r="B12" t="n">
-        <v>97763</v>
+        <v>96801</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1727,21 +1727,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219790</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1751,10 +1751,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>555097</v>
+        <v>555017</v>
       </c>
       <c r="R12" t="n">
-        <v>6954568</v>
+        <v>6954608</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1813,7 +1813,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118504909</v>
+        <v>118504907</v>
       </c>
       <c r="B13" t="n">
         <v>97867</v>
@@ -1853,10 +1853,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>555336</v>
+        <v>555127</v>
       </c>
       <c r="R13" t="n">
-        <v>6954786</v>
+        <v>6954603</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1915,10 +1915,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118504925</v>
+        <v>118504911</v>
       </c>
       <c r="B14" t="n">
-        <v>97763</v>
+        <v>97867</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1931,21 +1931,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1955,10 +1955,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>555051</v>
+        <v>555391</v>
       </c>
       <c r="R14" t="n">
-        <v>6954472</v>
+        <v>6954840</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2017,10 +2017,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118504907</v>
+        <v>118504925</v>
       </c>
       <c r="B15" t="n">
-        <v>97867</v>
+        <v>97763</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2033,21 +2033,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2057,10 +2057,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>555127</v>
+        <v>555051</v>
       </c>
       <c r="R15" t="n">
-        <v>6954603</v>
+        <v>6954472</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2119,10 +2119,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118504926</v>
+        <v>118504913</v>
       </c>
       <c r="B16" t="n">
-        <v>97763</v>
+        <v>97764</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2135,21 +2135,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219790</v>
+        <v>223591</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2159,10 +2159,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>554994</v>
+        <v>555342</v>
       </c>
       <c r="R16" t="n">
-        <v>6954526</v>
+        <v>6954794</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 43989-2023 artfynd.xlsx
+++ b/artfynd/A 43989-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118504914</v>
+        <v>118504912</v>
       </c>
       <c r="B2" t="n">
-        <v>97764</v>
+        <v>97771</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555352</v>
+        <v>555012</v>
       </c>
       <c r="R2" t="n">
-        <v>6954801</v>
+        <v>6954604</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118504927</v>
+        <v>118504921</v>
       </c>
       <c r="B3" t="n">
-        <v>101230</v>
+        <v>97770</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221343</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brunklöver</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Trifolium spadiceum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555116</v>
+        <v>555045</v>
       </c>
       <c r="R3" t="n">
-        <v>6954576</v>
+        <v>6954595</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118504915</v>
+        <v>118504927</v>
       </c>
       <c r="B4" t="n">
-        <v>97764</v>
+        <v>101237</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>223591</v>
+        <v>221343</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Brunklöver</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Trifolium spadiceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>555365</v>
+        <v>555116</v>
       </c>
       <c r="R4" t="n">
-        <v>6954814</v>
+        <v>6954576</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118504926</v>
+        <v>118504913</v>
       </c>
       <c r="B5" t="n">
-        <v>97763</v>
+        <v>97771</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>223591</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>554994</v>
+        <v>555342</v>
       </c>
       <c r="R5" t="n">
-        <v>6954526</v>
+        <v>6954794</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118504909</v>
+        <v>118504925</v>
       </c>
       <c r="B6" t="n">
-        <v>97867</v>
+        <v>97770</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>555336</v>
+        <v>555051</v>
       </c>
       <c r="R6" t="n">
-        <v>6954786</v>
+        <v>6954472</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118504912</v>
+        <v>118504914</v>
       </c>
       <c r="B7" t="n">
-        <v>97764</v>
+        <v>97771</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>555012</v>
+        <v>555352</v>
       </c>
       <c r="R7" t="n">
-        <v>6954604</v>
+        <v>6954801</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118504917</v>
+        <v>118504911</v>
       </c>
       <c r="B8" t="n">
-        <v>57718</v>
+        <v>97874</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,54 +1299,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103001</v>
+        <v>221952</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stormyran, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>555355</v>
+        <v>555391</v>
       </c>
       <c r="R8" t="n">
-        <v>6954810</v>
+        <v>6954840</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1405,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118504921</v>
+        <v>118504907</v>
       </c>
       <c r="B9" t="n">
-        <v>97763</v>
+        <v>97874</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1421,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1445,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>555045</v>
+        <v>555127</v>
       </c>
       <c r="R9" t="n">
-        <v>6954595</v>
+        <v>6954603</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1507,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118504924</v>
+        <v>118504915</v>
       </c>
       <c r="B10" t="n">
-        <v>97763</v>
+        <v>97771</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1523,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219790</v>
+        <v>223591</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1547,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>555097</v>
+        <v>555365</v>
       </c>
       <c r="R10" t="n">
-        <v>6954568</v>
+        <v>6954814</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1612,7 +1596,7 @@
         <v>118504920</v>
       </c>
       <c r="B11" t="n">
-        <v>96807</v>
+        <v>96814</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1711,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118504918</v>
+        <v>118504917</v>
       </c>
       <c r="B12" t="n">
-        <v>96801</v>
+        <v>57718</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1723,38 +1707,54 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>103001</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stormyran, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>555017</v>
+        <v>555355</v>
       </c>
       <c r="R12" t="n">
-        <v>6954608</v>
+        <v>6954810</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1813,10 +1813,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118504907</v>
+        <v>118504909</v>
       </c>
       <c r="B13" t="n">
-        <v>97867</v>
+        <v>97874</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1853,10 +1853,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>555127</v>
+        <v>555336</v>
       </c>
       <c r="R13" t="n">
-        <v>6954603</v>
+        <v>6954786</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1915,10 +1915,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118504911</v>
+        <v>118504918</v>
       </c>
       <c r="B14" t="n">
-        <v>97867</v>
+        <v>96808</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1931,21 +1931,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1955,10 +1955,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>555391</v>
+        <v>555017</v>
       </c>
       <c r="R14" t="n">
-        <v>6954840</v>
+        <v>6954608</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2017,10 +2017,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118504925</v>
+        <v>118504926</v>
       </c>
       <c r="B15" t="n">
-        <v>97763</v>
+        <v>97770</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2057,10 +2057,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>555051</v>
+        <v>554994</v>
       </c>
       <c r="R15" t="n">
-        <v>6954472</v>
+        <v>6954526</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2119,10 +2119,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118504913</v>
+        <v>118504924</v>
       </c>
       <c r="B16" t="n">
-        <v>97764</v>
+        <v>97770</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2135,21 +2135,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>223591</v>
+        <v>219790</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2159,10 +2159,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>555342</v>
+        <v>555097</v>
       </c>
       <c r="R16" t="n">
-        <v>6954794</v>
+        <v>6954568</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 43989-2023 artfynd.xlsx
+++ b/artfynd/A 43989-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118504912</v>
+        <v>118504921</v>
       </c>
       <c r="B2" t="n">
-        <v>97771</v>
+        <v>97770</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223591</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555012</v>
+        <v>555045</v>
       </c>
       <c r="R2" t="n">
-        <v>6954604</v>
+        <v>6954595</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118504921</v>
+        <v>118504925</v>
       </c>
       <c r="B3" t="n">
         <v>97770</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555045</v>
+        <v>555051</v>
       </c>
       <c r="R3" t="n">
-        <v>6954595</v>
+        <v>6954472</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118504913</v>
+        <v>118504909</v>
       </c>
       <c r="B5" t="n">
-        <v>97771</v>
+        <v>97874</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>223591</v>
+        <v>221952</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>555342</v>
+        <v>555336</v>
       </c>
       <c r="R5" t="n">
-        <v>6954794</v>
+        <v>6954786</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118504925</v>
+        <v>118504914</v>
       </c>
       <c r="B6" t="n">
-        <v>97770</v>
+        <v>97771</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219790</v>
+        <v>223591</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>555051</v>
+        <v>555352</v>
       </c>
       <c r="R6" t="n">
-        <v>6954472</v>
+        <v>6954801</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118504914</v>
+        <v>118504907</v>
       </c>
       <c r="B7" t="n">
-        <v>97771</v>
+        <v>97874</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>223591</v>
+        <v>221952</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>555352</v>
+        <v>555127</v>
       </c>
       <c r="R7" t="n">
-        <v>6954801</v>
+        <v>6954603</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118504911</v>
+        <v>118504920</v>
       </c>
       <c r="B8" t="n">
-        <v>97874</v>
+        <v>96814</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221952</v>
+        <v>221941</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>555391</v>
+        <v>555004</v>
       </c>
       <c r="R8" t="n">
-        <v>6954840</v>
+        <v>6954467</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118504907</v>
+        <v>118504924</v>
       </c>
       <c r="B9" t="n">
-        <v>97874</v>
+        <v>97770</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>555127</v>
+        <v>555097</v>
       </c>
       <c r="R9" t="n">
-        <v>6954603</v>
+        <v>6954568</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118504915</v>
+        <v>118504911</v>
       </c>
       <c r="B10" t="n">
-        <v>97771</v>
+        <v>97874</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>223591</v>
+        <v>221952</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>555365</v>
+        <v>555391</v>
       </c>
       <c r="R10" t="n">
-        <v>6954814</v>
+        <v>6954840</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118504920</v>
+        <v>118504926</v>
       </c>
       <c r="B11" t="n">
-        <v>96814</v>
+        <v>97770</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221941</v>
+        <v>219790</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>555004</v>
+        <v>554994</v>
       </c>
       <c r="R11" t="n">
-        <v>6954467</v>
+        <v>6954526</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118504917</v>
+        <v>118504912</v>
       </c>
       <c r="B12" t="n">
-        <v>57718</v>
+        <v>97771</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1707,54 +1707,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103001</v>
+        <v>223591</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stormyran, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>555355</v>
+        <v>555012</v>
       </c>
       <c r="R12" t="n">
-        <v>6954810</v>
+        <v>6954604</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1813,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118504909</v>
+        <v>118504918</v>
       </c>
       <c r="B13" t="n">
-        <v>97874</v>
+        <v>96808</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1829,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1853,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>555336</v>
+        <v>555017</v>
       </c>
       <c r="R13" t="n">
-        <v>6954786</v>
+        <v>6954608</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1915,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118504918</v>
+        <v>118504915</v>
       </c>
       <c r="B14" t="n">
-        <v>96808</v>
+        <v>97771</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1931,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>223591</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1955,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>555017</v>
+        <v>555365</v>
       </c>
       <c r="R14" t="n">
-        <v>6954608</v>
+        <v>6954814</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2017,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118504926</v>
+        <v>118504913</v>
       </c>
       <c r="B15" t="n">
-        <v>97770</v>
+        <v>97771</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2033,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219790</v>
+        <v>223591</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2057,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>554994</v>
+        <v>555342</v>
       </c>
       <c r="R15" t="n">
-        <v>6954526</v>
+        <v>6954794</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2119,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118504924</v>
+        <v>118504917</v>
       </c>
       <c r="B16" t="n">
-        <v>97770</v>
+        <v>57718</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2131,38 +2115,54 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219790</v>
+        <v>103001</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Stormyran, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>555097</v>
+        <v>555355</v>
       </c>
       <c r="R16" t="n">
-        <v>6954568</v>
+        <v>6954810</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 43989-2023 artfynd.xlsx
+++ b/artfynd/A 43989-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>118504917</v>
       </c>
       <c r="B2" t="n">
-        <v>57720</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58388</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,15 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118504907</v>
+        <v>118504921</v>
       </c>
       <c r="B3" t="n">
-        <v>97879</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -809,21 +799,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -833,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555127</v>
+        <v>555045</v>
       </c>
       <c r="R3" t="n">
-        <v>6954603</v>
+        <v>6954595</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,15 +885,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118504909</v>
+        <v>118504923</v>
       </c>
       <c r="B4" t="n">
-        <v>97879</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -911,21 +896,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -935,10 +920,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>555336</v>
+        <v>555153</v>
       </c>
       <c r="R4" t="n">
-        <v>6954786</v>
+        <v>6954584</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -997,15 +982,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118504926</v>
+        <v>118504924</v>
       </c>
       <c r="B5" t="n">
-        <v>97775</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1037,10 +1017,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>554994</v>
+        <v>555097</v>
       </c>
       <c r="R5" t="n">
-        <v>6954526</v>
+        <v>6954568</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,15 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118504911</v>
+        <v>118504925</v>
       </c>
       <c r="B6" t="n">
-        <v>97879</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1115,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>555391</v>
+        <v>555051</v>
       </c>
       <c r="R6" t="n">
-        <v>6954840</v>
+        <v>6954472</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1201,15 +1176,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118504915</v>
+        <v>118504926</v>
       </c>
       <c r="B7" t="n">
-        <v>97776</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1217,21 +1187,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>223591</v>
+        <v>219790</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1241,10 +1211,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>555365</v>
+        <v>554994</v>
       </c>
       <c r="R7" t="n">
-        <v>6954814</v>
+        <v>6954526</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1303,32 +1273,27 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118504920</v>
+        <v>118504927</v>
       </c>
       <c r="B8" t="n">
-        <v>96819</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102464</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221941</v>
+        <v>221343</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Brunklöver</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Trifolium spadiceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1343,10 +1308,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>555004</v>
+        <v>555116</v>
       </c>
       <c r="R8" t="n">
-        <v>6954467</v>
+        <v>6954576</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1405,15 +1370,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118504913</v>
+        <v>118504920</v>
       </c>
       <c r="B9" t="n">
-        <v>97776</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1421,21 +1381,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>223591</v>
+        <v>221941</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1445,10 +1405,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>555342</v>
+        <v>555004</v>
       </c>
       <c r="R9" t="n">
-        <v>6954794</v>
+        <v>6954467</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1510,12 +1470,7 @@
         <v>118504918</v>
       </c>
       <c r="B10" t="n">
-        <v>96813</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1609,15 +1564,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118504924</v>
+        <v>118504919</v>
       </c>
       <c r="B11" t="n">
-        <v>97775</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1625,21 +1575,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219790</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1649,10 +1599,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>555097</v>
+        <v>555424</v>
       </c>
       <c r="R11" t="n">
-        <v>6954568</v>
+        <v>6954915</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1711,15 +1661,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118504925</v>
+        <v>118504907</v>
       </c>
       <c r="B12" t="n">
-        <v>97775</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1727,21 +1672,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1751,10 +1696,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>555051</v>
+        <v>555127</v>
       </c>
       <c r="R12" t="n">
-        <v>6954472</v>
+        <v>6954603</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1813,15 +1758,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118504921</v>
+        <v>118504909</v>
       </c>
       <c r="B13" t="n">
-        <v>97775</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1829,21 +1769,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1853,10 +1793,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>555045</v>
+        <v>555336</v>
       </c>
       <c r="R13" t="n">
-        <v>6954595</v>
+        <v>6954786</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1915,15 +1855,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118504914</v>
+        <v>118504911</v>
       </c>
       <c r="B14" t="n">
-        <v>97776</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1931,21 +1866,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>223591</v>
+        <v>221952</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1955,10 +1890,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>555352</v>
+        <v>555391</v>
       </c>
       <c r="R14" t="n">
-        <v>6954801</v>
+        <v>6954840</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2020,12 +1955,7 @@
         <v>118504912</v>
       </c>
       <c r="B15" t="n">
-        <v>97776</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99036</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2119,37 +2049,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118504927</v>
+        <v>118504913</v>
       </c>
       <c r="B16" t="n">
-        <v>101242</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99036</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221343</v>
+        <v>223591</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brunklöver</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Trifolium spadiceum</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2159,10 +2084,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>555116</v>
+        <v>555342</v>
       </c>
       <c r="R16" t="n">
-        <v>6954576</v>
+        <v>6954794</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2218,6 +2143,200 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>118504914</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99036</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Stormyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>555352</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6954801</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-07-03</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-07-03</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>118504915</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99036</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Stormyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>555365</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6954814</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-07-03</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-07-03</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 43989-2023 artfynd.xlsx
+++ b/artfynd/A 43989-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -785,6 +790,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118504917</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118504921</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -979,6 +994,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118504923</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118504924</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1173,6 +1198,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118504925</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1270,6 +1300,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118504926</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1367,6 +1402,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118504927</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1464,6 +1504,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118504920</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1561,6 +1606,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118504918</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1658,6 +1708,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118504919</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1755,6 +1810,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118504907</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1852,6 +1912,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118504909</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1949,6 +2014,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118504911</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2046,6 +2116,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118504912</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2143,6 +2218,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118504913</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2240,6 +2320,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118504914</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2337,8 +2422,32 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118504915</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>